--- a/JO11-1/JO11-1_matchesDB.xlsx
+++ b/JO11-1/JO11-1_matchesDB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NLTSWIERZE\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C101A9FF-D140-4EC4-A5F9-54CF9C955B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990550DF-E5D7-4C81-A83D-0AA9AB389B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10605" yWindow="-21720" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MatchesDB" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="62">
   <si>
     <t>Matches</t>
   </si>
@@ -214,34 +214,37 @@
     <t>HSV de Zuidvogels JO 11-3</t>
   </si>
   <si>
-    <t>Victoria JO 11-4</t>
-  </si>
-  <si>
-    <t>NVC 11-2</t>
-  </si>
-  <si>
-    <t>SV Huizen 11-2</t>
-  </si>
-  <si>
     <t>1,1,1,0</t>
   </si>
   <si>
     <t>1,1,2,0</t>
   </si>
   <si>
-    <t>CTO '70 JO 11-1</t>
+    <t>NVC JO11-2</t>
   </si>
   <si>
-    <t>FC Amsterdam JO 11-2</t>
+    <t>Victoria JO11-4</t>
   </si>
   <si>
-    <t>Buitenveldert JO 11-3</t>
+    <t>SV Huizen JO11-2</t>
   </si>
   <si>
-    <t>Abcoude JO 11-2</t>
+    <t>CTO '70 JO11-1</t>
   </si>
   <si>
-    <t>Zuidoost United JO 11-1</t>
+    <t>FC Amsterdam JO11-2</t>
+  </si>
+  <si>
+    <t>Buitenveldert JO11-3</t>
+  </si>
+  <si>
+    <t>Abcoude JO11-2</t>
+  </si>
+  <si>
+    <t>Zuidoost United JO11-1</t>
+  </si>
+  <si>
+    <t>Biesbosch 39, 1115 HE Duivendrecht</t>
   </si>
 </sst>
 </file>
@@ -251,7 +254,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -304,6 +307,12 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -480,7 +489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -550,6 +559,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1281,7 +1293,7 @@
       </c>
       <c r="F12" s="22"/>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>31</v>
@@ -1329,7 +1341,7 @@
         <v>49</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="W12" s="6" t="s">
         <v>48</v>
@@ -1359,7 +1371,7 @@
       </c>
       <c r="F13" s="22"/>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>31</v>
@@ -1386,16 +1398,16 @@
         <v>49</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="Q13" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R13" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="S13" s="8" t="s">
         <v>49</v>
@@ -1404,7 +1416,7 @@
         <v>48</v>
       </c>
       <c r="U13" s="8" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="V13" s="8" t="s">
         <v>49</v>
@@ -1415,9 +1427,7 @@
       <c r="X13" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="Y13" s="6" t="s">
-        <v>47</v>
-      </c>
+      <c r="Y13" s="6"/>
       <c r="AD13" s="6"/>
     </row>
     <row r="14" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
@@ -1439,7 +1449,7 @@
       </c>
       <c r="F14" s="22"/>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>31</v>
@@ -1519,7 +1529,9 @@
       <c r="G15" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="H15" s="18"/>
+      <c r="H15" s="31" t="s">
+        <v>61</v>
+      </c>
       <c r="I15" s="18" t="s">
         <v>32</v>
       </c>
